--- a/tamu_data/evals/golden_sets/golden_20260411_v1_reworked6.xlsx
+++ b/tamu_data/evals/golden_sets/golden_20260411_v1_reworked6.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,6 +445,11 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>run:reworked6_20260412_20260412_053427</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>run:golden_20260411_v1_reworked6_20260412_20260412_102529</t>
         </is>
       </c>
     </row>
@@ -473,6 +478,11 @@
         </is>
       </c>
       <c r="F2" t="inlineStr">
+        <is>
+          <t>CSCE 608 §? 0.68, CSCE 605 §? 0.67, ISEN 620 §? 0.66, CSCE 614 §? 0.66, CSCE 635 §? 0.64, CSCE 713 §? 0.64, CSCE 681 §? 0.63, CSCE 681 §? 0.62, CSCE 629 §? 0.61, ISEN 620 §? 0.61</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>CSCE 608 §? 0.68, CSCE 605 §? 0.67, ISEN 620 §? 0.66, CSCE 614 §? 0.66, CSCE 635 §? 0.64, CSCE 713 §? 0.64, CSCE 681 §? 0.63, CSCE 681 §? 0.62, CSCE 629 §? 0.61, ISEN 620 §? 0.61</t>
         </is>
@@ -511,6 +521,11 @@
           <t>CSCE 638 §? 0.73, CSCE 670 §? 0.67, CSCE 641 §? 0.55, CSCE 633 §? 0.51, CSCE 726 §? 0.50, CSCE 726 §? 0.50, CSCE 605 §? 0.50, CSCE 726 §? 0.49, CSCE 665 §? 0.49, CSCE 638 §? 0.47</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>CSCE 638 §? 0.73, CSCE 670 §? 0.67, CSCE 641 §? 0.55, CSCE 633 §? 0.51, CSCE 726 §? 0.50, CSCE 726 §? 0.50, CSCE 605 §? 0.50, CSCE 726 §? 0.49, CSCE 665 §? 0.49, CSCE 638 §? 0.47</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -539,43 +554,22 @@
           <t>CSCE 632 §? 0.73, CSCE 624 §? 0.71, CSCE 633 §? 0.68, CSCE 614 §? 0.68, CSCE 624 §? 0.66, CSCE 726 §? 0.66, CSCE 641 §? 0.63, CSCE 748 §? 0.62, CSCE 670 §? 0.61, CSCE 605 §? 0.61</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CSCE 632 §? 0.73, CSCE 624 §? 0.71, CSCE 633 §? 0.68, CSCE 614 §? 0.68, CSCE 624 §? 0.66, CSCE 726 §? 0.66, CSCE 641 §? 0.63, CSCE 748 §? 0.62, CSCE 670 §? 0.61, CSCE 605 §? 0.61</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>What courses would you recommend taking after CSCE 632 to continue learning about HCl concepts?</t>
+          <t>How many programming projects are assigned in CSCE 611, and what do they cover? What are they about?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
-        <is>
-          <t>To continue learning about Human-Computer Interaction (HCI) concepts after CSCE 632, you might consider the following courses:
-CSCE 624: Sketch Recognition
-Description: This course is positioned at the "intersection of artificial intelligence, human–computer interaction, and visual communication". It delves into how humans sketch, how systems interpret sketches, and the behavior of recognition algorithms in real-world, noisy environments. The curriculum includes hands-on implementation of recognition techniques, critical analysis of research papers, and a semester-long team project.
-HCI Relevance: Students will learn to "design and conduct sketch-based experiments that account for human variability, interface design, and data collection constraints" and "critically read, interpret, and discuss research literature in sketch recognition and related AI/HCI domains".
-CSCE 635: Human-Centered Computing
-Description: While detailed course information is limited in the provided context, this course explicitly involves "human-centered considerations".
-HCI Relevance: The focus on "human-centered considerations" indicates a direct relevance to the principles and practices of Human-Computer Interaction.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>recursive</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>42</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>How many programming projects are assigned in CSCE 611, and what do they cover? What are they about?</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
         <is>
           <t>CSCE 611, section 600, includes a series of seven programming assignments, referred to as Machine Problems (MPs), which guide students through designing and developing a simple operating system .
 The topics covered by these assignments are:
@@ -588,38 +582,48 @@
 MP7: Journaled and Log-Based File Systems, Virtualization Introduction, Virtualization Mechanisms, and Memory Virtualization.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>CSCE 611 §? 0.59, CSCE 611 §? 0.51, CSCE 611 §? 0.50, CSCE 611 §? 0.43, CSCE 611 §? 0.25</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CSCE 611 §? 0.59, CSCE 611 §? 0.51, CSCE 611 §? 0.50, CSCE 611 §? 0.43, CSCE 611 §? 0.25</t>
+        </is>
+      </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="6">
+      <c r="A6" t="n">
         <v>45</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Does CSCE 611 have an explicit policy on the use of AI tools or generative AI for assignments?</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Yes, CSCE 611 has an explicit policy on the use of AI tools.
 For programming assignments, homework, and exams, students are explicitly prohibited from submitting or making use of AI-generated solutions or AI tools. The course emphasizes that the solution handed in must be the student's own, and this includes not using any part (code, text, figures, etc.) that has been developed by others, including AI. The course will use code-similarity detection tools and automated plagiarism detection tools, and any submission flagged by these tools will be treated as a potential violation.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CSCE 611 §? 0.68, CSCE 611 §? 0.59, CSCE 611 §? 0.39, CSCE 611 §? 0.25, CSCE 611 §? 0.17</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>CSCE 611 §? 0.68, CSCE 611 §? 0.59, CSCE 611 §? 0.39, CSCE 611 §? 0.25, CSCE 611 §? 0.17</t>
         </is>

--- a/tamu_data/evals/golden_sets/golden_20260411_v1_reworked6.xlsx
+++ b/tamu_data/evals/golden_sets/golden_20260411_v1_reworked6.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,6 +450,16 @@
       <c r="G1" t="inlineStr">
         <is>
           <t>run:golden_20260411_v1_reworked6_20260412_20260412_102529</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>run:flash_lite_threshold035_20260417_20260417_160416</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>run:reworked6_flash_lite_20260417_20260417_161027</t>
         </is>
       </c>
     </row>
@@ -485,6 +495,16 @@
       <c r="G2" t="inlineStr">
         <is>
           <t>CSCE 608 §? 0.68, CSCE 605 §? 0.67, ISEN 620 §? 0.66, CSCE 614 §? 0.66, CSCE 635 §? 0.64, CSCE 713 §? 0.64, CSCE 681 §? 0.63, CSCE 681 §? 0.62, CSCE 629 §? 0.61, ISEN 620 §? 0.61</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CSCE 605 §? 0.68, CSCE 681 §? 0.63, CSCE 713 §? 0.63, CSCE 629 §? 0.62, CSCE 681 §? 0.59, CSCE 652 §? 0.59, CSCE 614 §? 0.59, ISEN 620 §? 0.59, CSCE 635 §? 0.57, ISEN 620 §? 0.57</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>CSCE 605 §? 0.68, CSCE 681 §? 0.63, CSCE 713 §? 0.63, CSCE 629 §? 0.62, CSCE 681 §? 0.59, CSCE 652 §? 0.59, CSCE 614 §? 0.59, ISEN 620 §? 0.59, CSCE 635 §? 0.57, ISEN 620 §? 0.57</t>
         </is>
       </c>
     </row>
@@ -526,6 +546,16 @@
           <t>CSCE 638 §? 0.73, CSCE 670 §? 0.67, CSCE 641 §? 0.55, CSCE 633 §? 0.51, CSCE 726 §? 0.50, CSCE 726 §? 0.50, CSCE 605 §? 0.50, CSCE 726 §? 0.49, CSCE 665 §? 0.49, CSCE 638 §? 0.47</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CSCE 638 §? 0.72, CSCE 670 §? 0.61</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>CSCE 638 §? 0.72, CSCE 670 §? 0.61</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -557,6 +587,16 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>CSCE 632 §? 0.73, CSCE 624 §? 0.71, CSCE 633 §? 0.68, CSCE 614 §? 0.68, CSCE 624 §? 0.66, CSCE 726 §? 0.66, CSCE 641 §? 0.63, CSCE 748 §? 0.62, CSCE 670 §? 0.61, CSCE 605 §? 0.61</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CSCE 726 §? 0.70, CSCE 624 §? 0.68, CSCE 632 §? 0.68, CSCE 624 §? 0.67, CSCE 635 §? 0.67, CSCE 665 §? 0.67, CSCE 726 §? 0.63, CSCE 726 §? 0.61, CSCE 633 §? 0.59, CSCE 633 §? 0.59</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CSCE 726 §? 0.70, CSCE 624 §? 0.68, CSCE 632 §? 0.68, CSCE 624 §? 0.67, CSCE 635 §? 0.67, CSCE 665 §? 0.67, CSCE 726 §? 0.63, CSCE 726 §? 0.61, CSCE 633 §? 0.59, CSCE 633 §? 0.59</t>
         </is>
       </c>
     </row>
@@ -597,6 +637,16 @@
           <t>CSCE 611 §? 0.59, CSCE 611 §? 0.51, CSCE 611 §? 0.50, CSCE 611 §? 0.43, CSCE 611 §? 0.25</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CSCE 611 §? 0.54, CSCE 611 §? 0.51, CSCE 611 §? 0.51, CSCE 611 §? 0.46</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CSCE 611 §? 0.54, CSCE 611 §? 0.51, CSCE 611 §? 0.51, CSCE 611 §? 0.46</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -626,6 +676,16 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>CSCE 611 §? 0.68, CSCE 611 §? 0.59, CSCE 611 §? 0.39, CSCE 611 §? 0.25, CSCE 611 §? 0.17</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CSCE 611 §? 0.67, CSCE 611 §? 0.65</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CSCE 611 §? 0.67, CSCE 611 §? 0.65</t>
         </is>
       </c>
     </row>
